--- a/raw/Timetable_2026Autumn_2026CS.xlsx
+++ b/raw/Timetable_2026Autumn_2026CS.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB92505A-E026-42CE-8D17-6588E26A74DC}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACE114AC-5AF3-48D8-B244-4290F92DB7C3}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026CS1" sheetId="2" r:id="rId1"/>
     <sheet name="2026CS2" sheetId="3" r:id="rId2"/>
     <sheet name="2026CS3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -610,7 +609,7 @@
     <t>DING Pengyong</t>
   </si>
   <si>
-    <t>B309</t>
+    <t>B312</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1107,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -17333,13 +17332,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>